--- a/pdf2img/tabel/table_3.xlsx
+++ b/pdf2img/tabel/table_3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,12 +454,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PENGURUS</t>
+          <t>DEWAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>KOMISARIS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
@@ -475,63 +475,95 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEWAN</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOMISARIS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Komisaris</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Utama</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Dato’</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sri.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prof.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>DR.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Tahir,</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Komisaris</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Utama</t>
+          <t>Kemisaris</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dato’</t>
+          <t>Independen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sri.</t>
+          <t>.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Prof.</t>
+          <t>Ir.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DR.</t>
+          <t>Kumhal</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tahir,</t>
+          <t>Djamil,</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>S.E.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -541,27 +573,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Komisaris</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Independen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>:</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Drs.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Da'i</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bachtiar,</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>S.H.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>¥)</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>DEWAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DIREKSI</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -575,35 +643,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Komisaris</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Independen</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ir.</t>
+          <t>Utama</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Kumhal</t>
+          <t>:</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Djamil,</t>
+          <t>Hariyono</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$.E.</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
+          <t>Tiahjarijadi,</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MBA</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -612,15 +684,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wakil</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Birektur</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Utama</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>:</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Arifin</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -632,10 +728,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Direktur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rudy</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Mulyono</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -646,21 +758,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bachtiar,</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S.H.</t>
+          <t>Direktur</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Yohanes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Suhardi</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -671,29 +791,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Komisaris</t>
+          <t>PENGURUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Independen</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Drs.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Da'i</t>
-        </is>
-      </c>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -704,345 +812,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DEWAN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DIREKSI</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Utama</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Hariyono</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Tjahjarijadi,</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MBA</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Wakil</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Utama</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Arifin</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Rudy</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Mulyono</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Direktur</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Yohanes</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Suhardi</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>*)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
+          <t>*}</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Berlaku</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>efektif</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>setelah</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>mendapat</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>persetujuan</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>dari</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Otoritas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Qtoritas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Jasa</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Keuangan</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>(OJK).</t>
         </is>
